--- a/data/trans_orig/IP1002-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1002-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49056</t>
+          <t>48558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109197</t>
+          <t>109244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98408</t>
+          <t>98036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102492</t>
+          <t>102623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108106</t>
+          <t>108103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>203362</t>
+          <t>203662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209452</t>
+          <t>209651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69694</t>
+          <t>69436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74490</t>
+          <t>74521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147239</t>
+          <t>147016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153113</t>
+          <t>153146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36783</t>
+          <t>37372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41249</t>
+          <t>41250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80729</t>
+          <t>80664</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86071</t>
+          <t>86063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52146</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112241</t>
+          <t>112222</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125250</t>
+          <t>125001</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132235</t>
+          <t>131916</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258995</t>
+          <t>259864</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>6991</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>151013</t>
+          <t>150913</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>157139</t>
+          <t>156853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>155144</t>
+          <t>155457</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>162642</t>
+          <t>162129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>310270</t>
+          <t>309310</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>318294</t>
+          <t>318659</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>25768</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>666028</t>
+          <t>665636</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>676066</t>
+          <t>675450</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>708725</t>
+          <t>707937</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>718307</t>
+          <t>717875</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1376281</t>
+          <t>1377953</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1391723</t>
+          <t>1391325</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46693</t>
+          <t>46134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>52138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56642</t>
+          <t>55751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105944</t>
+          <t>105397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112417</t>
+          <t>112371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98408</t>
+          <t>98426</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104082</t>
+          <t>104078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105992</t>
+          <t>106046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110536</t>
+          <t>110540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207031</t>
+          <t>207627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213972</t>
+          <t>214009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63233</t>
+          <t>63880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65154</t>
+          <t>64817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69941</t>
+          <t>69939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131028</t>
+          <t>131074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137404</t>
+          <t>137435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76363</t>
+          <t>76734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81607</t>
+          <t>81601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154034</t>
+          <t>153457</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159360</t>
+          <t>159366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39345</t>
+          <t>40352</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36672</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43748</t>
+          <t>43917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79145</t>
+          <t>78964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87589</t>
+          <t>87258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>51652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54269</t>
+          <t>54182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59533</t>
+          <t>59546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108799</t>
+          <t>109285</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115453</t>
+          <t>115497</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132702</t>
+          <t>132057</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138051</t>
+          <t>138053</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139319</t>
+          <t>138967</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145079</t>
+          <t>145073</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>274618</t>
+          <t>274680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282419</t>
+          <t>282446</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167381</t>
+          <t>166989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332173</t>
+          <t>332233</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27606</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>37721</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>689904</t>
+          <t>689410</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>700970</t>
+          <t>700506</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>720536</t>
+          <t>721945</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>735507</t>
+          <t>736536</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1416315</t>
+          <t>1417349</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1433952</t>
+          <t>1434564</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>53504</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60539</t>
+          <t>60189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116845</t>
+          <t>116688</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121350</t>
+          <t>121333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100766</t>
+          <t>101113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103250</t>
+          <t>103291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109027</t>
+          <t>109032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206569</t>
+          <t>205509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212951</t>
+          <t>212362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63299</t>
+          <t>63323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133517</t>
+          <t>132960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73166</t>
+          <t>73533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77402</t>
+          <t>78036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152843</t>
+          <t>154034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85401</t>
+          <t>86168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51166</t>
+          <t>50845</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52201</t>
+          <t>53902</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107783</t>
+          <t>107742</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132779</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139349</t>
+          <t>139764</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>275494</t>
+          <t>275085</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>564</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158498</t>
+          <t>158644</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>163576</t>
+          <t>163612</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162964</t>
+          <t>163268</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>169602</t>
+          <t>169555</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>324953</t>
+          <t>324458</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>332396</t>
+          <t>332427</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,47 +10173,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>17791</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>11636</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>25341</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>17791</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>12131</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>25866</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>691713</t>
+          <t>690782</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>700379</t>
+          <t>700220</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>728432</t>
+          <t>728537</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>738887</t>
+          <t>738753</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,47 +10286,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1431424</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1423874</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1437579</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>99,2%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1431424</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1423349</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1437084</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74371</t>
+          <t>75146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147209</t>
+          <t>147598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121929</t>
+          <t>121702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123859</t>
+          <t>123581</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>248072</t>
+          <t>248348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>253071</t>
+          <t>253106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54799</t>
+          <t>55142</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122385</t>
+          <t>121795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64024</t>
+          <t>64536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142762</t>
+          <t>142277</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53110</t>
+          <t>53074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99412</t>
+          <t>98372</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>21152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114863</t>
+          <t>114897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122366</t>
+          <t>122373</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138507</t>
+          <t>139468</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>152273</t>
+          <t>151810</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258619</t>
+          <t>259368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>272957</t>
+          <t>272931</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>126899</t>
+          <t>127262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>283401</t>
+          <t>283527</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>29264</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>650470</t>
+          <t>649859</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>660691</t>
+          <t>660303</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>742313</t>
+          <t>741603</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>755132</t>
+          <t>755294</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1397991</t>
+          <t>1397045</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1414725</t>
+          <t>1413377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
